--- a/Budget.xlsx
+++ b/Budget.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jhrg/src/opendap/ESDS_AI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0DFF9792-A7FB-E047-A3E9-C50ED0804A00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4778064D-799A-F849-A415-100F9FDCAA98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="18920" yWindow="1400" windowWidth="28040" windowHeight="17180" xr2:uid="{5EE2F73C-A965-2049-AC5D-3BBF6DF8A5C1}"/>
   </bookViews>
@@ -39,23 +39,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
     <t>Who</t>
   </si>
   <si>
-    <t>months</t>
-  </si>
-  <si>
-    <t>cost</t>
-  </si>
-  <si>
     <t>James Gallagher</t>
   </si>
   <si>
-    <t>hourly rate</t>
-  </si>
-  <si>
     <t>hours/month</t>
   </si>
   <si>
@@ -74,7 +65,19 @@
     <t>Ed Armstrong</t>
   </si>
   <si>
-    <t>monthly cost</t>
+    <t>Hourly rate</t>
+  </si>
+  <si>
+    <t>Months</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>Monthly cost</t>
+  </si>
+  <si>
+    <t>n/a</t>
   </si>
 </sst>
 </file>
@@ -126,16 +129,43 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -474,121 +504,129 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.1640625" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="1"/>
-    <col min="5" max="5" width="10.83203125" style="2"/>
+    <col min="2" max="2" width="10.83203125" style="8"/>
+    <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="B1" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
         <v>1</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
-        <v>3</v>
       </c>
       <c r="B2" s="7">
         <v>220.15</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="12">
         <v>167</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="12">
         <v>2</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="13">
         <f>D2*C2*B2</f>
         <v>73530.100000000006</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="4">
+    <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6">
         <v>199.07</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="14">
         <v>167</v>
       </c>
-      <c r="D3" s="3">
-        <v>3</v>
-      </c>
-      <c r="E3" s="5">
+      <c r="D3" s="14">
+        <v>2</v>
+      </c>
+      <c r="E3" s="15">
         <f>D3*C3*B3</f>
-        <v>99734.069999999992</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
-        <v>10</v>
+        <v>66489.38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="B4" s="7">
         <v>220.15</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="12">
         <v>167</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="12">
         <v>1</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="13">
         <f>D4*C4*B4</f>
         <v>36765.050000000003</v>
       </c>
     </row>
-    <row r="5" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="4" t="s">
+    <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="5"/>
-    </row>
-    <row r="6" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
-        <v>7</v>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="B6" s="7">
         <v>2500</v>
       </c>
-      <c r="D6" s="6">
+      <c r="C6" s="12"/>
+      <c r="D6" s="12">
         <v>4</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="13">
         <f>D6*B6</f>
         <v>10000</v>
       </c>
     </row>
-    <row r="7" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="E7" s="5"/>
-    </row>
-    <row r="8" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="7"/>
-      <c r="E8" s="8"/>
-    </row>
-    <row r="9" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="E9" s="5">
+      <c r="E8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="E9" s="3">
         <f>SUM(E2:E8)</f>
-        <v>220029.21999999997</v>
+        <v>186784.53000000003</v>
       </c>
     </row>
   </sheetData>
